--- a/Sajjad data/by_country_and_state/Canada/QC.xlsx
+++ b/Sajjad data/by_country_and_state/Canada/QC.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="809">
   <si>
     <t>Business Name</t>
   </si>
@@ -1427,6 +1427,1017 @@
   </si>
   <si>
     <t>2026-10-26T19:09:35.664Z</t>
+  </si>
+  <si>
+    <t>Laboratoire Dentaire Pro-Fixe Estrie</t>
+  </si>
+  <si>
+    <t>+1 819-563-1296</t>
+  </si>
+  <si>
+    <t>872 Rue Homère, Sherbrooke, QC J1N 2H8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Laboratoire+Dentaire+Pro-Fixe+Estrie/data=!4m7!3m6!1s0x4cb64b15382dd6ef:0x7363197ed3b8c524!8m2!3d45.3660279!4d-71.9829404!16s%2Fg%2F1th6dfzy!19sChIJ79YtOBVLtkwRJMW4034ZY3M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:36:45.289Z</t>
+  </si>
+  <si>
+    <t>Carenne Lavalleare Inc</t>
+  </si>
+  <si>
+    <t>+1 819-569-3445</t>
+  </si>
+  <si>
+    <t>1855 Boul de Portland Bur 200, Sherbrooke, QC J1J 3V7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Carenne+Lavalleare+Inc/data=!4m7!3m6!1s0x4cb7b364bf76e1b7:0xeef61181ac96f260!8m2!3d45.4040882!4d-71.9200832!16s%2Fg%2F11b5wq5652!19sChIJt-F2v2Szt0wRYPKWrIER9u4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:36:47.246Z</t>
+  </si>
+  <si>
+    <t>Supplied</t>
+  </si>
+  <si>
+    <t>+1 514-224-6000</t>
+  </si>
+  <si>
+    <t>1615 Rue Brûlotte, Sherbrooke, QC J1E 3P4, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–8:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Supplied/data=!4m7!3m6!1s0x4cb7b30287e804c9:0xcafa6b08da85af48!8m2!3d45.4287527!4d-71.8709567!16s%2Fg%2F11vq94h8nx!19sChIJyQTohwKzt0wRSK-F2ghr-so?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:36:49.502Z</t>
+  </si>
+  <si>
+    <t>Halley Wellet</t>
+  </si>
+  <si>
+    <t>+1 819-563-8018</t>
+  </si>
+  <si>
+    <t>1051 Rue du Conseil, Sherbrooke, QC J1G 1M1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Halley+Wellet/data=!4m7!3m6!1s0x4cb7b2fdd920e381:0x377bf204b3fb885!8m2!3d45.4039325!4d-71.8659889!16s%2Fg%2F1v29bmhm!19sChIJgeMg2f2yt0wRhbg_SyC_dwM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:36:51.356Z</t>
+  </si>
+  <si>
+    <t>Lemay Laurent Dr</t>
+  </si>
+  <si>
+    <t>+1 819-566-5722</t>
+  </si>
+  <si>
+    <t>75 Rue Wellington N, Sherbrooke, QC J1H 5A9, Canada</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lemay+Laurent+Dr/data=!4m7!3m6!1s0x4cb7b30faa3652c1:0x4037f5fb8e07ea16!8m2!3d45.4025605!4d-71.8913321!16s%2Fg%2F1td5l94y!19sChIJwVI2qg-zt0wRFuoHjvv1N0A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:36:52.871Z</t>
+  </si>
+  <si>
+    <t>Claude Lefebvre</t>
+  </si>
+  <si>
+    <t>+1 819-569-2339</t>
+  </si>
+  <si>
+    <t>1000 Rue Hamelin, Sherbrooke, QC J1G 3B5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Claude+Lefebvre/data=!4m7!3m6!1s0x4cb7b2ebc5208329:0x845f205175062afe!8m2!3d45.3895135!4d-71.8608198!16s%2Fg%2F11b5wrrxm6!19sChIJKYMgxeuyt0wR_ioGdVEgX4Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:36:54.922Z</t>
+  </si>
+  <si>
+    <t>Laboratoire Dentaire J L Inc</t>
+  </si>
+  <si>
+    <t>+1 819-565-5226</t>
+  </si>
+  <si>
+    <t>5640 Chem. Blanchette, Sherbrooke, QC J1N 0C9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Laboratoire+Dentaire+J+L+Inc/data=!4m7!3m6!1s0x4cb7b4f1f4a22e79:0xc1c082f730676973!8m2!3d45.334281!4d-71.9995239!16s%2Fg%2F1tkqzwbf!19sChIJeS6i9PG0t0wRc2lnMPeCwME?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:36:57.373Z</t>
+  </si>
+  <si>
+    <t>Mitnyan Charles L Dr</t>
+  </si>
+  <si>
+    <t>+1 819-563-4848</t>
+  </si>
+  <si>
+    <t>250 Rue King E, Sherbrooke, QC J1G 1A9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mitnyan+Charles+L+Dr/data=!4m7!3m6!1s0x4cb7b306526d7d0b:0xe691e750989e0abe!8m2!3d45.4059524!4d-71.8830099!16s%2Fg%2F1tk8bqs0!19sChIJC31tUgazt0wRvgqemFDnkeY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:36:59.428Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire Du Rond-Point</t>
+  </si>
+  <si>
+    <t>+1 418-838-9188</t>
+  </si>
+  <si>
+    <t>40 Rte du Président-Kennedy, Lévis, QC G6V 6C4, Canada</t>
+  </si>
+  <si>
+    <t>Lévis</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Du+Rond-Point/data=!4m7!3m6!1s0x4cb895ae87267c13:0x5c58aa5a41c7f48f!8m2!3d46.7968264!4d-71.1793587!16s%2Fg%2F11ddwt2scb!19sChIJE3wmh66VuEwRj_THQVqqWFw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:37:29.301Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire Patrice Russell</t>
+  </si>
+  <si>
+    <t>+1 418-835-6228</t>
+  </si>
+  <si>
+    <t>5801 Bd Wilfrid-Carrier Ste 403, Lévis, QC G6V 0C9, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–12 PM1:30–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Patrice+Russell/data=!4m7!3m6!1s0x4cb8958ec4e4aeaf:0xf86fb75c72f645f9!8m2!3d46.7871992!4d-71.1583717!16s%2Fg%2F1vk6yv31!19sChIJr67kxI6VuEwR-UX2cly3b_g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:37:30.976Z</t>
+  </si>
+  <si>
+    <t>Dr André Chamberland</t>
+  </si>
+  <si>
+    <t>+1 418-835-7339</t>
+  </si>
+  <si>
+    <t>Oral surgeon</t>
+  </si>
+  <si>
+    <t>143 Rue Wolfe, Lévis, QC G6V 3Z1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Andr%C3%A9+Chamberland/data=!4m7!3m6!1s0x4cb895946d663acf:0xb098533d4d7b1d62!8m2!3d46.8146202!4d-71.1767006!16s%2Fg%2F11b6qftdvh!19sChIJzzpmbZSVuEwRYh17TT1TmLA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:37:32.554Z</t>
+  </si>
+  <si>
+    <t>Laboratoire dentaire Marcel Marcoux Inc</t>
+  </si>
+  <si>
+    <t>+1 418-833-1259</t>
+  </si>
+  <si>
+    <t>11 Av. Bégin, Lévis, QC G6V 4B6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Laboratoire+dentaire+Marcel+Marcoux+Inc/data=!4m7!3m6!1s0x4cb895b954343eeb:0xd17a77f9ceaab85e!8m2!3d46.8068524!4d-71.1834628!16s%2Fg%2F11b5wl63by!19sChIJ6z40VLmVuEwRXriqzvl3etE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:37:35.045Z</t>
+  </si>
+  <si>
+    <t>Dr Wilson François</t>
+  </si>
+  <si>
+    <t>+1 418-835-7332</t>
+  </si>
+  <si>
+    <t>143 Rue Wolfe, Lévis, QC G6V 3Z7, Canada</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Wilson+Fran%C3%A7ois/data=!4m7!3m6!1s0x4cb895946d663acf:0x47d81473853e558b!8m2!3d46.8145821!4d-71.1772867!16s%2Fg%2F11b6bqfvx2!19sChIJzzpmbZSVuEwRi1U-hXMU2Ec?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:37:36.822Z</t>
+  </si>
+  <si>
+    <t>André Lavoie</t>
+  </si>
+  <si>
+    <t>+1 418-837-2833</t>
+  </si>
+  <si>
+    <t>5500 Rte du Président-Kennedy, Lévis, QC G6V 4Z2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Andr%C3%A9+Lavoie/data=!4m7!3m6!1s0x4cb89501d19e386d:0x3f382f6e7e5ff784!8m2!3d46.7942225!4d-71.1774698!16s%2Fg%2F1wh4fgcq!19sChIJbTie0QGVuEwRhPdffm4vOD8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:37:39.564Z</t>
+  </si>
+  <si>
+    <t>Emilie Carrier DDS</t>
+  </si>
+  <si>
+    <t>+1 418-833-3352</t>
+  </si>
+  <si>
+    <t>17 Rue Cauchy, Lévis, QC G6V 5C8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emilie+Carrier+DDS/data=!4m7!3m6!1s0x4cb895938b052d97:0xa41c7c81369a085d!8m2!3d46.8164021!4d-71.1783398!16s%2Fg%2F11b5wkpl2k!19sChIJly0Fi5OVuEwRXQiaNoF8HKQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:37:41.313Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire Sylvain Labrecque</t>
+  </si>
+  <si>
+    <t>+1 418-881-3383</t>
+  </si>
+  <si>
+    <t>428A Rte 273, Saint-Apollinaire, Quebec G0S 2E0, Canada</t>
+  </si>
+  <si>
+    <t>Saint-Apollinaire</t>
+  </si>
+  <si>
+    <t>Monday8:30 AM–4:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Sylvain+Labrecque/data=!4m7!3m6!1s0x4cb8865175eeae2d:0x99bd046d025b236d!8m2!3d46.6135231!4d-71.5117618!16s%2Fg%2F1tlwf7lq!19sChIJLa7udVGGuEwRbSNbAm0EvZk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:38:01.270Z</t>
+  </si>
+  <si>
+    <t>Marc Morissette</t>
+  </si>
+  <si>
+    <t>+1 418-832-7178</t>
+  </si>
+  <si>
+    <t>3756-A Av. des Églises, Charny, QC G6X 1X4, Canada</t>
+  </si>
+  <si>
+    <t>Charny</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Marc+Morissette/data=!4m7!3m6!1s0x4cb8922e52e332d3:0xede9a70284405913!8m2!3d46.7204531!4d-71.266768!16s%2Fg%2F11b5wqb9jc!19sChIJ0zLjUi6SuEwRE1lAhAKn6e0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:38:48.480Z</t>
+  </si>
+  <si>
+    <t>Miclette &amp; Dion Dentistes</t>
+  </si>
+  <si>
+    <t>+1 418-547-9381</t>
+  </si>
+  <si>
+    <t>2407 Rue Saint-Dominique, Jonquière, QC G7X 6L1, Canada</t>
+  </si>
+  <si>
+    <t>Jonquière</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Miclette+%26+Dion+Dentistes/data=!4m7!3m6!1s0x4cc029202bc48ec3:0x7e512e5e4d446947!8m2!3d48.4129629!4d-71.2540253!16s%2Fg%2F1tdc07hj!19sChIJw47EKyApwEwRR2lETV4uUX4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:22.221Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire François Mc Nicoll</t>
+  </si>
+  <si>
+    <t>+1 418-673-4637</t>
+  </si>
+  <si>
+    <t>3521 Bd Martel Suite 200, Saint-Honoré, QC G0V 1L0, Canada</t>
+  </si>
+  <si>
+    <t>Saint-Honoré</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Fran%C3%A7ois+Mc+Nicoll/data=!4m7!3m6!1s0x4cea9b5990e369d7:0xc191453bce766b0!8m2!3d48.5335566!4d-71.0866761!16s%2Fg%2F1ts_672c!19sChIJ12njkFmb6kwRsGbnvFMUGQw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:23.776Z</t>
+  </si>
+  <si>
+    <t>Pierre Martel</t>
+  </si>
+  <si>
+    <t>+1 418-548-2133</t>
+  </si>
+  <si>
+    <t>2792 Rue de la Salle, Saguenay, QC G7S 2A4, Canada</t>
+  </si>
+  <si>
+    <t>Saguenay</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pierre+Martel/data=!4m7!3m6!1s0x4cc027d51f7e320b:0x4fd3d4e3458c5e2e!8m2!3d48.4217441!4d-71.1777744!16s%2Fg%2F11b5wlny99!19sChIJCzJ-H9UnwEwRLl6MRePU008?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:25.563Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire Claude Jean</t>
+  </si>
+  <si>
+    <t>+1 418-695-3337</t>
+  </si>
+  <si>
+    <t>2334 Rue Saint-Dominique, Jonquière, QC G7X 6L8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Claude+Jean/data=!4m7!3m6!1s0x4cc0291f3190e533:0x77a7b577af34836e!8m2!3d48.4143192!4d-71.2537587!16s%2Fg%2F11b5wjmr0n!19sChIJM-WQMR8pwEwRboM0r3e1p3c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:27.330Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire Nadia Bergeron</t>
+  </si>
+  <si>
+    <t>+1 418-544-5931</t>
+  </si>
+  <si>
+    <t>1344 Rue Bagot, La Baie, QC G7B 2P4, Canada</t>
+  </si>
+  <si>
+    <t>La Baie</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Nadia+Bergeron/data=!4m7!3m6!1s0x4cc01eaf05104171:0xa420c0af6c36581b!8m2!3d48.3377189!4d-70.8860738!16s%2Fg%2F1td586lz!19sChIJcUEQBa8ewEwRG1g2bK_AIKQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:29.051Z</t>
+  </si>
+  <si>
+    <t>Laboratoire Dentaire Boreal</t>
+  </si>
+  <si>
+    <t>+1 418-545-7023</t>
+  </si>
+  <si>
+    <t>3670 Rang Saint-Pierre, Chicoutimi, QC G7H 0E6, Canada</t>
+  </si>
+  <si>
+    <t>Chicoutimi</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Laboratoire+Dentaire+Boreal/data=!4m7!3m6!1s0x4cc020ceaaaaaaab:0x2bd63d69768d7e1e!8m2!3d48.3628035!4d-71.1556951!16s%2Fg%2F1tl_lb1l!19sChIJq6qqqs4gwEwRHn6Ndmk91is?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:30.938Z</t>
+  </si>
+  <si>
+    <t>Denis Dauchon DDS</t>
+  </si>
+  <si>
+    <t>+1 418-543-4330</t>
+  </si>
+  <si>
+    <t>2181 Bd de Tadoussac, Chicoutimi, QC G7G 4X2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denis+Dauchon+DDS/data=!4m7!3m6!1s0x4cc0275736df02c1:0x1a2fbc7ba26d5417!8m2!3d48.4371489!4d-71.0611871!16s%2Fg%2F11b5wtgqp2!19sChIJwQLfNlcnwEwRF1Rtonu8Lxo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:33.443Z</t>
+  </si>
+  <si>
+    <t>Dion Gismond Dr</t>
+  </si>
+  <si>
+    <t>+1 418-543-8802</t>
+  </si>
+  <si>
+    <t>58 Rue Racine O, Chicoutimi, QC G7J 1E2, Canada</t>
+  </si>
+  <si>
+    <t>Monday8:30 AM–12 PM1–7:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dion+Gismond+Dr/data=!4m7!3m6!1s0x4cc0274f545ef965:0xc5dd178a793f6138!8m2!3d48.4279567!4d-71.0702691!16s%2Fg%2F1td_4s_9!19sChIJZfleVE8nwEwROGE_eYoX3cU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:35.169Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire De L'Anse</t>
+  </si>
+  <si>
+    <t>+1 418-272-3368</t>
+  </si>
+  <si>
+    <t>Rue de l'Anse, L'Anse-Saint-Jean, QC G0V 1J0, Canada</t>
+  </si>
+  <si>
+    <t>L'Anse-Saint-Jean</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+De+L%27Anse/data=!4m7!3m6!1s0x4cc029ee06e75aad:0xb8b3af302ce582a6!8m2!3d48.460287!4d-71.260107!16s%2Fg%2F11b5w8893c!19sChIJrVrnBu4pwEwRpoLlLDCvs7g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:37.060Z</t>
+  </si>
+  <si>
+    <t>Clinique Morency Dntrlgsts</t>
+  </si>
+  <si>
+    <t>+1 418-817-3551</t>
+  </si>
+  <si>
+    <t>105 Bd de la Grande Baie N, La Baie, QC G7B 3K1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Morency+Dntrlgsts/data=!4m7!3m6!1s0x4cc01ea8dd29499d:0xc3801b7a428cc502!8m2!3d48.3354038!4d-70.8816793!16s%2Fg%2F11b5wjhtht!19sChIJnUkp3agewEwRAsWMQnobgMM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:38.536Z</t>
+  </si>
+  <si>
+    <t>Marcel Munger</t>
+  </si>
+  <si>
+    <t>+1 418-545-7397</t>
+  </si>
+  <si>
+    <t>874 Bd de l'Université, Chicoutimi, QC G7H 6B6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Marcel+Munger/data=!4m7!3m6!1s0x4cc020c92d3ccc57:0x611e3ff3c650ca20!8m2!3d48.4150581!4d-71.0543275!16s%2Fg%2F1tgnwv40!19sChIJV8w8LckgwEwRIMpQxvM_HmE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:40.384Z</t>
+  </si>
+  <si>
+    <t>Denturologiste Dany Fortin</t>
+  </si>
+  <si>
+    <t>+1 418-545-1099</t>
+  </si>
+  <si>
+    <t>80 Rue Racine E Unit 214, Chicoutimi, Quebec G7H 1P6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denturologiste+Dany+Fortin/data=!4m7!3m6!1s0x4cc0279ede8e58b1:0xa946209778732030!8m2!3d48.4279049!4d-71.0656054!16s%2Fg%2F11t4y_tswt!19sChIJsViO3p4nwEwRMCBzeJcgRqk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:42.250Z</t>
+  </si>
+  <si>
+    <t>Guy Boivin Denturologiste</t>
+  </si>
+  <si>
+    <t>+1 418-543-7097</t>
+  </si>
+  <si>
+    <t>920 Boul. Sainte-Geneviève, Chicoutimi, QC G7G 2G4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Guy+Boivin+Denturologiste/data=!4m7!3m6!1s0x4cea9d8884901b81:0x5edddb1263d41f5f!8m2!3d48.4494693!4d-71.0859894!16s%2Fg%2F1tf0q7m3!19sChIJgRuQhIid6kwRXx_UYxLb3V4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:44.198Z</t>
+  </si>
+  <si>
+    <t>Complexe Dentaire Du Saguenay</t>
+  </si>
+  <si>
+    <t>+1 418-541-7032</t>
+  </si>
+  <si>
+    <t>Medical clinic</t>
+  </si>
+  <si>
+    <t>110 Bd Barrette, Chicoutimi, QC G7H 6X6, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Complexe+Dentaire+Du+Saguenay/data=!4m7!3m6!1s0x4cc026d348518e73:0xf453814859d5bfdd!8m2!3d48.3970241!4d-71.0777204!16s%2Fg%2F1tfk_tpy!19sChIJc45RSNMmwEwR3b_VWUiBU_Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:55.744Z</t>
+  </si>
+  <si>
+    <t>Stephanie Lepage DDS</t>
+  </si>
+  <si>
+    <t>+1 418-696-1545</t>
+  </si>
+  <si>
+    <t>990 Rue Bégin, Chicoutimi, QC G7H 5X2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stephanie+Lepage+DDS/data=!4m7!3m6!1s0x4cc02732977be1c7:0x1575af11fa961c53!8m2!3d48.4129465!4d-71.0682644!16s%2Fg%2F1hc23z469!19sChIJx-F7lzInwEwRUxyW-hGvdRU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:39:57.148Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire Elysee</t>
+  </si>
+  <si>
+    <t>+1 418-690-9613</t>
+  </si>
+  <si>
+    <t>463 Rue Des Champs-Élysées, Chicoutimi, QC G7H 5V7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Elysee/data=!4m7!3m6!1s0x4cc020d0366d3093:0x6ec0c83b6e9461af!8m2!3d48.4090118!4d-71.056221!16s%2Fg%2F1tfk40z5!19sChIJkzBtNtAgwEwRr2GUbjvIwG4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:40:13.280Z</t>
+  </si>
+  <si>
+    <t>Le Shack Beauté</t>
+  </si>
+  <si>
+    <t>+1 581-306-5485</t>
+  </si>
+  <si>
+    <t>2196 Rue Saint-Dominique, Jonquière, QC G7X 6M3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Le+Shack+Beaut%C3%A9/data=!4m7!3m6!1s0x4cc028e057d02497:0x28e5135ab60ad3d1!8m2!3d48.4179685!4d-71.2505916!16s%2Fg%2F11fnwh4n53!19sChIJlyTQV-AowEwR0dMKtloT5Sg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:40:14.910Z</t>
+  </si>
+  <si>
+    <t>Complex Medical Axe Saguenay</t>
+  </si>
+  <si>
+    <t>+1 418-545-3505</t>
+  </si>
+  <si>
+    <t>Medical Center</t>
+  </si>
+  <si>
+    <t>484 Bd du Royaume O local 210, Chicoutimi, QC G7H 0S7, Canada</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Complex+Medical+Axe+Saguenay/data=!4m7!3m6!1s0x4cc0270b02707d5b:0xa74d5c08b5025d01!8m2!3d48.3821578!4d-71.0889595!16s%2Fg%2F11pq679cvk!19sChIJW31wAgsnwEwRAV0CtQhcTac?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:40:33.903Z</t>
+  </si>
+  <si>
+    <t>Centre d'autonomie Familiprix Chicoutimi</t>
+  </si>
+  <si>
+    <t>+1 418-542-1255</t>
+  </si>
+  <si>
+    <t>Wheelchair store</t>
+  </si>
+  <si>
+    <t>690 R. des Actionnaires, Chicoutimi, QC G7J 5A8, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–12 PM1–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Centre+d%27autonomie+Familiprix+Chicoutimi/data=!4m7!3m6!1s0x4cc026dda968ccc5:0x1c0225da58786025!8m2!3d48.3997906!4d-71.1016583!16s%2Fg%2F11c1q8bxck!19sChIJxcxoqd0mwEwRJWB4WNolAhw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:40:35.478Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire Dr Pierre Bourgeois</t>
+  </si>
+  <si>
+    <t>+1 819-375-1551</t>
+  </si>
+  <si>
+    <t>143 Rue Radisson #1, Trois-Rivières, QC G9A 2C5, Canada</t>
+  </si>
+  <si>
+    <t>Trois-Rivières</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Dr+Pierre+Bourgeois/data=!4m7!3m6!1s0x4cc7c603f9a2f8f3:0x63f1c906c9cc3ac8!8m2!3d46.3426041!4d-72.5409049!16s%2Fg%2F1tfgn__l!19sChIJ8_ii-QPGx0wRyDrMyQbJ8WM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:18.386Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire Du Dr</t>
+  </si>
+  <si>
+    <t>+1 819-693-3388</t>
+  </si>
+  <si>
+    <t>1220 Rue Jean Nicolet, Trois-Rivières, QC G9A 1B2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Du+Dr/data=!4m7!3m6!1s0x4cc7c8a06b61d553:0xa614c49ab3afe0ff!8m2!3d46.3558739!4d-72.5405845!16s%2Fg%2F11b5wpcshp!19sChIJU9Vha6DIx0wR_-Cvs5rEFKY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:20.132Z</t>
+  </si>
+  <si>
+    <t>Blais Marc Dr</t>
+  </si>
+  <si>
+    <t>+1 819-371-3620</t>
+  </si>
+  <si>
+    <t>1020 Bd des Récollets, Trois-Rivières, QC G8Z 3X1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Blais+Marc+Dr/data=!4m7!3m6!1s0x4cc7c920ec96a077:0x92a5ecdd124b3067!8m2!3d46.3578419!4d-72.5732993!16s%2Fg%2F1tmxqmcy!19sChIJd6CW7CDJx0wRZzBLEt3spZI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:21.724Z</t>
+  </si>
+  <si>
+    <t>Centre Dentaire Marie-Claude Michaud</t>
+  </si>
+  <si>
+    <t>+1 819-909-4906</t>
+  </si>
+  <si>
+    <t>2505 Bd Thibeau, Trois-Rivières, QC G8T 1G1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Centre+Dentaire+Marie-Claude+Michaud/data=!4m7!3m6!1s0x4cc7c9dcecfd8d9b:0x77dc31f76660f0a!8m2!3d46.4144418!4d-72.581047!16s%2Fg%2F11b5wfnb_m!19sChIJm4397NzJx0wRCg9mdh_DfQc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:24.691Z</t>
+  </si>
+  <si>
+    <t>Danielle Trottier Denturologiste</t>
+  </si>
+  <si>
+    <t>+1 819-370-1916</t>
+  </si>
+  <si>
+    <t>1181 des Forges, Trois-Rivières, Quebec G8Z 1T7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Danielle+Trottier+Denturologiste/data=!4m7!3m6!1s0x4cc7c9d8e7a8a78f:0x23493de7ae5dd3c1!8m2!3d46.3441304!4d-72.5538867!16s%2Fg%2F11spx8fn06!19sChIJj6eo59jJx0wRwdNdruc9SSM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:26.679Z</t>
+  </si>
+  <si>
+    <t>Denturologiste Milot</t>
+  </si>
+  <si>
+    <t>+1 819-376-6325</t>
+  </si>
+  <si>
+    <t>580 Rue Barkoff, Trois-Rivières, QC G8T 9T7, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denturologiste+Milot/data=!4m7!3m6!1s0x4cc7c88a91a8368f:0x95996dc343b4267f!8m2!3d46.3775704!4d-72.5517874!16s%2Fg%2F1tj4b27j!19sChIJjzaokYrIx0wRfya0Q8NtmZU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:28.432Z</t>
+  </si>
+  <si>
+    <t>Perron Jean-Pierre Dr</t>
+  </si>
+  <si>
+    <t>+1 819-373-4480</t>
+  </si>
+  <si>
+    <t>5065 Bd des Forges, Trois-Rivières, QC G8Y 4Z3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Perron+Jean-Pierre+Dr/data=!4m7!3m6!1s0x4cc7c920ebbf02af:0xbf89ada165b49cdb!8m2!3d46.3612887!4d-72.5935496!16s%2Fg%2F1td1_wjb!19sChIJrwK_6yDJx0wR25y0ZaGtib8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:30.367Z</t>
+  </si>
+  <si>
+    <t>Centre Médical &amp; Dentaire</t>
+  </si>
+  <si>
+    <t>+1 819-376-1144</t>
+  </si>
+  <si>
+    <t>5495 Boulevard Jean-XXIII, Trois-Rivières, Quebec G8Z 4A8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Centre+M%C3%A9dical+%26+Dentaire/data=!4m7!3m6!1s0x4cc7cf3a785e23dd:0xb8f163e578fa442e!8m2!3d46.3348227!4d-72.5898585!16s%2Fg%2F11b5w9hztj!19sChIJ3SNeeDrPx0wRLkT6eOVj8bg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:32.149Z</t>
+  </si>
+  <si>
+    <t>Plante Pierre-Yvon</t>
+  </si>
+  <si>
+    <t>+1 819-375-3930</t>
+  </si>
+  <si>
+    <t>3575 Rue de Cherbourg, Trois-Rivières, QC G8Y 5V9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Plante+Pierre-Yvon/data=!4m7!3m6!1s0x4cc7ced79b5791ad:0x2140336bc848bcee!8m2!3d46.3384451!4d-72.6091355!16s%2Fg%2F1v_smvvn!19sChIJrZFXm9fOx0wR7rxIyGszQCE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:33.815Z</t>
+  </si>
+  <si>
+    <t>COOP HD QUÉBEC</t>
+  </si>
+  <si>
+    <t>+1 819-979-2697</t>
+  </si>
+  <si>
+    <t>1060 Rue St François Xavier #125, Trois-Rivières, QC G9A 1R8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/COOP+HD+QU%C3%89BEC/data=!4m7!3m6!1s0x4cc7c60047e17927:0x1d6447af7332fea4!8m2!3d46.3507459!4d-72.5453872!16s%2Fg%2F11mgmbyqr7!19sChIJJ3nhRwDGx0wRpP4yc69HZB0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:35.585Z</t>
+  </si>
+  <si>
+    <t>Laboratoire Dentaire 3R</t>
+  </si>
+  <si>
+    <t>+1 819-448-5333</t>
+  </si>
+  <si>
+    <t>1435 12e, Trois-Rivières, QC G8Y 3A1, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Laboratoire+Dentaire+3R/data=!4m7!3m6!1s0x4cc7c8c40b2d38db:0xc1e2efdfdb14c85b!8m2!3d46.3629129!4d-72.5946663!16s%2Fg%2F11j00rx3h0!19sChIJ2zgtC8TIx0wRW8gU29_v4sE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:40.290Z</t>
+  </si>
+  <si>
+    <t>Clinique De Chirurgie Buccale</t>
+  </si>
+  <si>
+    <t>+1 819-379-6263</t>
+  </si>
+  <si>
+    <t>2915 Rue Gagnon, Trois-Rivières, QC G8Z 3Z4, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+De+Chirurgie+Buccale/data=!4m7!3m6!1s0x4cc7cf3a53070623:0x68f602045bb197cc!8m2!3d46.3328235!4d-72.5914776!16s%2Fg%2F11b5wk_www!19sChIJIwYHUzrPx0wRzJexWwQC9mg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:41.814Z</t>
+  </si>
+  <si>
+    <t>Dental Clinic Malo Clinic</t>
+  </si>
+  <si>
+    <t>+1 819-694-4506</t>
+  </si>
+  <si>
+    <t>dental clinic</t>
+  </si>
+  <si>
+    <t>3050 Bd Saint-Jean, Trois-Rivières, QC G9B 2M9, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Clinic+Malo+Clinic/data=!4m7!3m6!1s0x4cc7cf22cb954dfb:0x4a5e4e53318fae98!8m2!3d46.3281732!4d-72.5988084!16s%2Fg%2F11b5wpvxh3!19sChIJ-02VyyLPx0wRmK6PMVNOXko?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:43.362Z</t>
+  </si>
+  <si>
+    <t>Mario Gendron DDS</t>
+  </si>
+  <si>
+    <t>+1 819-373-1313</t>
+  </si>
+  <si>
+    <t>4870 Bd des Forges, Trois-Rivières, QC G8Y 1W9, Canada</t>
+  </si>
+  <si>
+    <t>Monday8 AM–9 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mario+Gendron+DDS/data=!4m7!3m6!1s0x4cc7c8cd5c46fa91:0xdcea472f7190a997!8m2!3d46.3608999!4d-72.5915249!16s%2Fg%2F1ptyy29ww!19sChIJkfpGXM3Ix0wRl6mQcS9H6tw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:41:55.143Z</t>
+  </si>
+  <si>
+    <t>La Griffe Santé</t>
+  </si>
+  <si>
+    <t>+1 819-840-2690</t>
+  </si>
+  <si>
+    <t>Pet supply store</t>
+  </si>
+  <si>
+    <t>1626 6e Rue, Trois-Rivières, QC G8Y 5B8, Canada</t>
+  </si>
+  <si>
+    <t>Monday9:30 AM–5:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/La+Griffe+Sant%C3%A9/data=!4m7!3m6!1s0x4cc7c94848d4fe25:0xf8cdc6b2cf34f074!8m2!3d46.3592164!4d-72.5920408!16s%2Fg%2F11fhrghwy_!19sChIJJf7USEjJx0wRdPA0z7LGzfg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:42:03.970Z</t>
+  </si>
+  <si>
+    <t>Clini Plus</t>
+  </si>
+  <si>
+    <t>+1 819-372-0848</t>
+  </si>
+  <si>
+    <t>Pharmacy</t>
+  </si>
+  <si>
+    <t>5050 Bd des Forges, Trois-Rivières, QC G8Y 1X2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clini+Plus/data=!4m7!3m6!1s0x4cc7c92093b2e11b:0xf934b3e3faf6210d!8m2!3d46.3618848!4d-72.592833!16s%2Fg%2F11b5wrbffr!19sChIJG-GykyDJx0wRDSH2-uOzNPk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:42:16.363Z</t>
+  </si>
+  <si>
+    <t>Centre Dentaire Côté</t>
+  </si>
+  <si>
+    <t>+1 450-492-4030</t>
+  </si>
+  <si>
+    <t>1740 Chem. Saint-Charles #201, Terrebonne, Quebec J6W 3R3, Canada</t>
+  </si>
+  <si>
+    <t>Terrebonne</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Centre+Dentaire+C%C3%B4t%C3%A9/data=!4m7!3m6!1s0x4cc8de22b146574d:0xaac7e055901bbaf8!8m2!3d45.6955556!4d-73.6149023!16s%2Fg%2F1trttyc7!19sChIJTVdGsSLeyEwR-LobkFXgx6o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:43:24.432Z</t>
+  </si>
+  <si>
+    <t>Clinique Dentaire Chantal Cloutier</t>
+  </si>
+  <si>
+    <t>+1 450-477-2222</t>
+  </si>
+  <si>
+    <t>5171 Bd Laurier Bur 201, Terrebonne, QC J7M 1W2, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+Dentaire+Chantal+Cloutier/data=!4m7!3m6!1s0x4cc8dbb9328b2183:0xbb3502f3babea4d!8m2!3d45.7521879!4d-73.706552!16s%2Fg%2F1tgw9j5h!19sChIJgyGLMrnbyEwRTeqrOy9Qsws?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:43:25.963Z</t>
+  </si>
+  <si>
+    <t>Clinique HD La Chaise</t>
+  </si>
+  <si>
+    <t>+1 514-999-8821</t>
+  </si>
+  <si>
+    <t>762 Boul Terrebonne, Terrebonne, Quebec J6W 2H3, Canada</t>
+  </si>
+  <si>
+    <t>Monday9 AM–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinique+HD+La+Chaise/data=!4m7!3m6!1s0x4cc91983ac5b0ab9:0x17b5553d06398abc!8m2!3d45.7014181!4d-73.629825!16s%2Fg%2F11nmpppwh6!19sChIJuQpbrIMZyUwRvIo5Bj1VtRc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:43:27.810Z</t>
+  </si>
+  <si>
+    <t>Francois Bourdeau</t>
+  </si>
+  <si>
+    <t>+1 450-474-0666</t>
+  </si>
+  <si>
+    <t>2694 Ch Sainte-Marie, Mascouche, QC J7K 1M9, Canada</t>
+  </si>
+  <si>
+    <t>Mascouche</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Francois+Bourdeau/data=!4m7!3m6!1s0x4cc8dda96b2509cd:0x69b9d22d3d16aede!8m2!3d45.7514564!4d-73.6122848!16s%2Fg%2F11b5wfg0g6!19sChIJzQkla6ndyEwR3q4WPS3SuWk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:43:39.299Z</t>
+  </si>
+  <si>
+    <t>Confection De Protheses Dent</t>
+  </si>
+  <si>
+    <t>+1 450-964-4848</t>
+  </si>
+  <si>
+    <t>500 Bd des Seigneurs #204, Terrebonne, Quebec J6W 1T3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Confection+De+Protheses+Dent/data=!4m7!3m6!1s0x4cc8de68c4204473:0x47f4d4c2558be38d!8m2!3d45.7036368!4d-73.6331156!16s%2Fg%2F11b5wfg2m4!19sChIJc0QgxGjeyEwRjeOLVcLU9Ec?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:43:41.128Z</t>
+  </si>
+  <si>
+    <t>Laboratoire dentaire Gagnon</t>
+  </si>
+  <si>
+    <t>+1 514-224-4720</t>
+  </si>
+  <si>
+    <t>1050 Rue des Fontaines, Mascouche, Quebec J7K 0V3, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Laboratoire+dentaire+Gagnon/data=!4m7!3m6!1s0x4cc8ddfe452ea58d:0x9c254e7b546bbc2f!8m2!3d45.7314588!4d-73.6338882!16s%2Fg%2F11klt2h7py!19sChIJjaUuRf7dyEwRL7xrVHtOJZw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:43:42.677Z</t>
+  </si>
+  <si>
+    <t>Destination Dentaire Mascouche - Kids &amp; Family Emergency Dental Care</t>
+  </si>
+  <si>
+    <t>+1 514-218-5300</t>
+  </si>
+  <si>
+    <t>155 Mnt Masson, Mascouche, QC J7K 0A8, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Destination+Dentaire+Mascouche+-+Kids+%26+Family+Emergency+Dental+Care/data=!4m7!3m6!1s0x4cc8dddd731abaeb:0x37afb5468b0c6192!8m2!3d45.7236619!4d-73.6115241!16s%2Fg%2F11hblqtqbt!19sChIJ67oac93dyEwRkmEMi0a1rzc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:43:49.711Z</t>
+  </si>
+  <si>
+    <t>Blanc Pure</t>
+  </si>
+  <si>
+    <t>+1 514-891-8819</t>
+  </si>
+  <si>
+    <t>170 Mnt Masson, Mascouche, QC J7K 3B5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Blanc+Pure/data=!4m7!3m6!1s0x4cc8ddc783cd724d:0xc549f7537ab4ca25!8m2!3d45.7247974!4d-73.6209307!16s%2Fg%2F11lkgzhysp!19sChIJTXLNg8fdyEwRJcq0elP3ScU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:44:00.904Z</t>
+  </si>
+  <si>
+    <t>jobmed</t>
+  </si>
+  <si>
+    <t>(855) 325-2299</t>
+  </si>
+  <si>
+    <t>Emergency dental service</t>
+  </si>
+  <si>
+    <t>400 Mnt Masson local 2, Mascouche, QC J7K 2L5, Canada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/jobmed/data=!4m7!3m6!1s0x4cc8ddc5cda4211b:0x21f01d7f9698551f!8m2!3d45.7305319!4d-73.6164282!16s%2Fg%2F12mkvn5z_!19sChIJGyGkzcXdyEwRH1WYln8d8CE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-26T23:44:27.903Z</t>
   </si>
 </sst>
 </file>
@@ -1807,7 +2818,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M75"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -4899,6 +5910,2507 @@
         <v>471</v>
       </c>
     </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>472</v>
+      </c>
+      <c r="B76" t="s">
+        <v>473</v>
+      </c>
+      <c r="C76" t="s">
+        <v>151</v>
+      </c>
+      <c r="D76" t="s">
+        <v>474</v>
+      </c>
+      <c r="E76" t="s">
+        <v>431</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>51</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>64</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>475</v>
+      </c>
+      <c r="M76" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>477</v>
+      </c>
+      <c r="B77" t="s">
+        <v>478</v>
+      </c>
+      <c r="C77" t="s">
+        <v>28</v>
+      </c>
+      <c r="D77" t="s">
+        <v>479</v>
+      </c>
+      <c r="E77" t="s">
+        <v>431</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>64</v>
+      </c>
+      <c r="I77" t="s">
+        <v>211</v>
+      </c>
+      <c r="J77" t="s">
+        <v>64</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>480</v>
+      </c>
+      <c r="M77" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>482</v>
+      </c>
+      <c r="B78" t="s">
+        <v>483</v>
+      </c>
+      <c r="C78" t="s">
+        <v>468</v>
+      </c>
+      <c r="D78" t="s">
+        <v>484</v>
+      </c>
+      <c r="E78" t="s">
+        <v>431</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>64</v>
+      </c>
+      <c r="I78" t="s">
+        <v>211</v>
+      </c>
+      <c r="J78" t="s">
+        <v>485</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>486</v>
+      </c>
+      <c r="M78" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>488</v>
+      </c>
+      <c r="B79" t="s">
+        <v>489</v>
+      </c>
+      <c r="C79" t="s">
+        <v>28</v>
+      </c>
+      <c r="D79" t="s">
+        <v>490</v>
+      </c>
+      <c r="E79" t="s">
+        <v>431</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>64</v>
+      </c>
+      <c r="I79" t="s">
+        <v>211</v>
+      </c>
+      <c r="J79" t="s">
+        <v>64</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>491</v>
+      </c>
+      <c r="M79" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>493</v>
+      </c>
+      <c r="B80" t="s">
+        <v>494</v>
+      </c>
+      <c r="C80" t="s">
+        <v>28</v>
+      </c>
+      <c r="D80" t="s">
+        <v>495</v>
+      </c>
+      <c r="E80" t="s">
+        <v>431</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>496</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>64</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>497</v>
+      </c>
+      <c r="M80" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>499</v>
+      </c>
+      <c r="B81" t="s">
+        <v>500</v>
+      </c>
+      <c r="C81" t="s">
+        <v>28</v>
+      </c>
+      <c r="D81" t="s">
+        <v>501</v>
+      </c>
+      <c r="E81" t="s">
+        <v>431</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>64</v>
+      </c>
+      <c r="I81" t="s">
+        <v>211</v>
+      </c>
+      <c r="J81" t="s">
+        <v>64</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>502</v>
+      </c>
+      <c r="M81" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>504</v>
+      </c>
+      <c r="B82" t="s">
+        <v>505</v>
+      </c>
+      <c r="C82" t="s">
+        <v>151</v>
+      </c>
+      <c r="D82" t="s">
+        <v>506</v>
+      </c>
+      <c r="E82" t="s">
+        <v>431</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>64</v>
+      </c>
+      <c r="I82" t="s">
+        <v>211</v>
+      </c>
+      <c r="J82" t="s">
+        <v>362</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>507</v>
+      </c>
+      <c r="M82" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>509</v>
+      </c>
+      <c r="B83" t="s">
+        <v>510</v>
+      </c>
+      <c r="C83" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" t="s">
+        <v>511</v>
+      </c>
+      <c r="E83" t="s">
+        <v>431</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>64</v>
+      </c>
+      <c r="I83" t="s">
+        <v>211</v>
+      </c>
+      <c r="J83" t="s">
+        <v>64</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>512</v>
+      </c>
+      <c r="M83" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>514</v>
+      </c>
+      <c r="B84" t="s">
+        <v>515</v>
+      </c>
+      <c r="C84" t="s">
+        <v>28</v>
+      </c>
+      <c r="D84" t="s">
+        <v>516</v>
+      </c>
+      <c r="E84" t="s">
+        <v>517</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>518</v>
+      </c>
+      <c r="I84" t="s">
+        <v>21</v>
+      </c>
+      <c r="J84" t="s">
+        <v>324</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>519</v>
+      </c>
+      <c r="M84" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>521</v>
+      </c>
+      <c r="B85" t="s">
+        <v>522</v>
+      </c>
+      <c r="C85" t="s">
+        <v>28</v>
+      </c>
+      <c r="D85" t="s">
+        <v>523</v>
+      </c>
+      <c r="E85" t="s">
+        <v>517</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>20</v>
+      </c>
+      <c r="I85" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s">
+        <v>524</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>525</v>
+      </c>
+      <c r="M85" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>527</v>
+      </c>
+      <c r="B86" t="s">
+        <v>528</v>
+      </c>
+      <c r="C86" t="s">
+        <v>529</v>
+      </c>
+      <c r="D86" t="s">
+        <v>530</v>
+      </c>
+      <c r="E86" t="s">
+        <v>517</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>51</v>
+      </c>
+      <c r="I86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s">
+        <v>64</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>531</v>
+      </c>
+      <c r="M86" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>533</v>
+      </c>
+      <c r="B87" t="s">
+        <v>534</v>
+      </c>
+      <c r="C87" t="s">
+        <v>151</v>
+      </c>
+      <c r="D87" t="s">
+        <v>535</v>
+      </c>
+      <c r="E87" t="s">
+        <v>517</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
+        <v>64</v>
+      </c>
+      <c r="I87" t="s">
+        <v>211</v>
+      </c>
+      <c r="J87" t="s">
+        <v>64</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" t="s">
+        <v>536</v>
+      </c>
+      <c r="M87" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>538</v>
+      </c>
+      <c r="B88" t="s">
+        <v>539</v>
+      </c>
+      <c r="C88" t="s">
+        <v>529</v>
+      </c>
+      <c r="D88" t="s">
+        <v>540</v>
+      </c>
+      <c r="E88" t="s">
+        <v>517</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>541</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s">
+        <v>64</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" t="s">
+        <v>542</v>
+      </c>
+      <c r="M88" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>544</v>
+      </c>
+      <c r="B89" t="s">
+        <v>545</v>
+      </c>
+      <c r="C89" t="s">
+        <v>28</v>
+      </c>
+      <c r="D89" t="s">
+        <v>546</v>
+      </c>
+      <c r="E89" t="s">
+        <v>517</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" t="s">
+        <v>64</v>
+      </c>
+      <c r="I89" t="s">
+        <v>211</v>
+      </c>
+      <c r="J89" t="s">
+        <v>64</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>547</v>
+      </c>
+      <c r="M89" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>549</v>
+      </c>
+      <c r="B90" t="s">
+        <v>550</v>
+      </c>
+      <c r="C90" t="s">
+        <v>28</v>
+      </c>
+      <c r="D90" t="s">
+        <v>551</v>
+      </c>
+      <c r="E90" t="s">
+        <v>517</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>64</v>
+      </c>
+      <c r="I90" t="s">
+        <v>211</v>
+      </c>
+      <c r="J90" t="s">
+        <v>64</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>552</v>
+      </c>
+      <c r="M90" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>554</v>
+      </c>
+      <c r="B91" t="s">
+        <v>555</v>
+      </c>
+      <c r="C91" t="s">
+        <v>28</v>
+      </c>
+      <c r="D91" t="s">
+        <v>556</v>
+      </c>
+      <c r="E91" t="s">
+        <v>557</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" t="s">
+        <v>51</v>
+      </c>
+      <c r="I91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s">
+        <v>558</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" t="s">
+        <v>559</v>
+      </c>
+      <c r="M91" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>561</v>
+      </c>
+      <c r="B92" t="s">
+        <v>562</v>
+      </c>
+      <c r="C92" t="s">
+        <v>28</v>
+      </c>
+      <c r="D92" t="s">
+        <v>563</v>
+      </c>
+      <c r="E92" t="s">
+        <v>564</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" t="s">
+        <v>51</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s">
+        <v>64</v>
+      </c>
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" t="s">
+        <v>565</v>
+      </c>
+      <c r="M92" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>567</v>
+      </c>
+      <c r="B93" t="s">
+        <v>568</v>
+      </c>
+      <c r="C93" t="s">
+        <v>28</v>
+      </c>
+      <c r="D93" t="s">
+        <v>569</v>
+      </c>
+      <c r="E93" t="s">
+        <v>570</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>293</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>463</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" t="s">
+        <v>571</v>
+      </c>
+      <c r="M93" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>573</v>
+      </c>
+      <c r="B94" t="s">
+        <v>574</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" t="s">
+        <v>575</v>
+      </c>
+      <c r="E94" t="s">
+        <v>576</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" t="s">
+        <v>293</v>
+      </c>
+      <c r="I94" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s">
+        <v>58</v>
+      </c>
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" t="s">
+        <v>577</v>
+      </c>
+      <c r="M94" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>579</v>
+      </c>
+      <c r="B95" t="s">
+        <v>580</v>
+      </c>
+      <c r="C95" t="s">
+        <v>28</v>
+      </c>
+      <c r="D95" t="s">
+        <v>581</v>
+      </c>
+      <c r="E95" t="s">
+        <v>582</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" t="s">
+        <v>64</v>
+      </c>
+      <c r="I95" t="s">
+        <v>211</v>
+      </c>
+      <c r="J95" t="s">
+        <v>64</v>
+      </c>
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" t="s">
+        <v>583</v>
+      </c>
+      <c r="M95" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>585</v>
+      </c>
+      <c r="B96" t="s">
+        <v>586</v>
+      </c>
+      <c r="C96" t="s">
+        <v>28</v>
+      </c>
+      <c r="D96" t="s">
+        <v>587</v>
+      </c>
+      <c r="E96" t="s">
+        <v>570</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>51</v>
+      </c>
+      <c r="I96" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s">
+        <v>64</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" t="s">
+        <v>588</v>
+      </c>
+      <c r="M96" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>590</v>
+      </c>
+      <c r="B97" t="s">
+        <v>591</v>
+      </c>
+      <c r="C97" t="s">
+        <v>28</v>
+      </c>
+      <c r="D97" t="s">
+        <v>592</v>
+      </c>
+      <c r="E97" t="s">
+        <v>593</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>89</v>
+      </c>
+      <c r="I97" t="s">
+        <v>21</v>
+      </c>
+      <c r="J97" t="s">
+        <v>153</v>
+      </c>
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" t="s">
+        <v>594</v>
+      </c>
+      <c r="M97" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>596</v>
+      </c>
+      <c r="B98" t="s">
+        <v>597</v>
+      </c>
+      <c r="C98" t="s">
+        <v>151</v>
+      </c>
+      <c r="D98" t="s">
+        <v>598</v>
+      </c>
+      <c r="E98" t="s">
+        <v>599</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" t="s">
+        <v>51</v>
+      </c>
+      <c r="I98" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s">
+        <v>64</v>
+      </c>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" t="s">
+        <v>600</v>
+      </c>
+      <c r="M98" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>602</v>
+      </c>
+      <c r="B99" t="s">
+        <v>603</v>
+      </c>
+      <c r="C99" t="s">
+        <v>28</v>
+      </c>
+      <c r="D99" t="s">
+        <v>604</v>
+      </c>
+      <c r="E99" t="s">
+        <v>599</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" t="s">
+        <v>64</v>
+      </c>
+      <c r="I99" t="s">
+        <v>211</v>
+      </c>
+      <c r="J99" t="s">
+        <v>64</v>
+      </c>
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" t="s">
+        <v>605</v>
+      </c>
+      <c r="M99" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>607</v>
+      </c>
+      <c r="B100" t="s">
+        <v>608</v>
+      </c>
+      <c r="C100" t="s">
+        <v>28</v>
+      </c>
+      <c r="D100" t="s">
+        <v>609</v>
+      </c>
+      <c r="E100" t="s">
+        <v>599</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>64</v>
+      </c>
+      <c r="I100" t="s">
+        <v>211</v>
+      </c>
+      <c r="J100" t="s">
+        <v>610</v>
+      </c>
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" t="s">
+        <v>611</v>
+      </c>
+      <c r="M100" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>613</v>
+      </c>
+      <c r="B101" t="s">
+        <v>614</v>
+      </c>
+      <c r="C101" t="s">
+        <v>28</v>
+      </c>
+      <c r="D101" t="s">
+        <v>615</v>
+      </c>
+      <c r="E101" t="s">
+        <v>616</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
+        <v>64</v>
+      </c>
+      <c r="I101" t="s">
+        <v>211</v>
+      </c>
+      <c r="J101" t="s">
+        <v>64</v>
+      </c>
+      <c r="K101" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" t="s">
+        <v>617</v>
+      </c>
+      <c r="M101" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>619</v>
+      </c>
+      <c r="B102" t="s">
+        <v>620</v>
+      </c>
+      <c r="C102" t="s">
+        <v>28</v>
+      </c>
+      <c r="D102" t="s">
+        <v>621</v>
+      </c>
+      <c r="E102" t="s">
+        <v>593</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
+        <v>64</v>
+      </c>
+      <c r="I102" t="s">
+        <v>211</v>
+      </c>
+      <c r="J102" t="s">
+        <v>64</v>
+      </c>
+      <c r="K102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" t="s">
+        <v>622</v>
+      </c>
+      <c r="M102" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>624</v>
+      </c>
+      <c r="B103" t="s">
+        <v>625</v>
+      </c>
+      <c r="C103" t="s">
+        <v>28</v>
+      </c>
+      <c r="D103" t="s">
+        <v>626</v>
+      </c>
+      <c r="E103" t="s">
+        <v>599</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" t="s">
+        <v>64</v>
+      </c>
+      <c r="I103" t="s">
+        <v>211</v>
+      </c>
+      <c r="J103" t="s">
+        <v>64</v>
+      </c>
+      <c r="K103" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103" t="s">
+        <v>627</v>
+      </c>
+      <c r="M103" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>629</v>
+      </c>
+      <c r="B104" t="s">
+        <v>630</v>
+      </c>
+      <c r="C104" t="s">
+        <v>299</v>
+      </c>
+      <c r="D104" t="s">
+        <v>631</v>
+      </c>
+      <c r="E104" t="s">
+        <v>599</v>
+      </c>
+      <c r="F104" t="s">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" t="s">
+        <v>64</v>
+      </c>
+      <c r="I104" t="s">
+        <v>395</v>
+      </c>
+      <c r="J104" t="s">
+        <v>64</v>
+      </c>
+      <c r="K104" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104" t="s">
+        <v>632</v>
+      </c>
+      <c r="M104" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>634</v>
+      </c>
+      <c r="B105" t="s">
+        <v>635</v>
+      </c>
+      <c r="C105" t="s">
+        <v>28</v>
+      </c>
+      <c r="D105" t="s">
+        <v>636</v>
+      </c>
+      <c r="E105" t="s">
+        <v>599</v>
+      </c>
+      <c r="F105" t="s">
+        <v>18</v>
+      </c>
+      <c r="G105" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" t="s">
+        <v>317</v>
+      </c>
+      <c r="I105" t="s">
+        <v>21</v>
+      </c>
+      <c r="J105" t="s">
+        <v>362</v>
+      </c>
+      <c r="K105" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" t="s">
+        <v>637</v>
+      </c>
+      <c r="M105" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>639</v>
+      </c>
+      <c r="B106" t="s">
+        <v>640</v>
+      </c>
+      <c r="C106" t="s">
+        <v>641</v>
+      </c>
+      <c r="D106" t="s">
+        <v>642</v>
+      </c>
+      <c r="E106" t="s">
+        <v>599</v>
+      </c>
+      <c r="F106" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" t="s">
+        <v>64</v>
+      </c>
+      <c r="I106" t="s">
+        <v>211</v>
+      </c>
+      <c r="J106" t="s">
+        <v>64</v>
+      </c>
+      <c r="K106" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106" t="s">
+        <v>643</v>
+      </c>
+      <c r="M106" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>645</v>
+      </c>
+      <c r="B107" t="s">
+        <v>646</v>
+      </c>
+      <c r="C107" t="s">
+        <v>28</v>
+      </c>
+      <c r="D107" t="s">
+        <v>647</v>
+      </c>
+      <c r="E107" t="s">
+        <v>599</v>
+      </c>
+      <c r="F107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" t="s">
+        <v>64</v>
+      </c>
+      <c r="I107" t="s">
+        <v>211</v>
+      </c>
+      <c r="J107" t="s">
+        <v>64</v>
+      </c>
+      <c r="K107" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107" t="s">
+        <v>648</v>
+      </c>
+      <c r="M107" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>650</v>
+      </c>
+      <c r="B108" t="s">
+        <v>651</v>
+      </c>
+      <c r="C108" t="s">
+        <v>28</v>
+      </c>
+      <c r="D108" t="s">
+        <v>652</v>
+      </c>
+      <c r="E108" t="s">
+        <v>599</v>
+      </c>
+      <c r="F108" t="s">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" t="s">
+        <v>89</v>
+      </c>
+      <c r="I108" t="s">
+        <v>21</v>
+      </c>
+      <c r="J108" t="s">
+        <v>369</v>
+      </c>
+      <c r="K108" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108" t="s">
+        <v>653</v>
+      </c>
+      <c r="M108" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>655</v>
+      </c>
+      <c r="B109" t="s">
+        <v>656</v>
+      </c>
+      <c r="C109" t="s">
+        <v>468</v>
+      </c>
+      <c r="D109" t="s">
+        <v>657</v>
+      </c>
+      <c r="E109" t="s">
+        <v>570</v>
+      </c>
+      <c r="F109" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" t="s">
+        <v>64</v>
+      </c>
+      <c r="I109" t="s">
+        <v>211</v>
+      </c>
+      <c r="J109" t="s">
+        <v>90</v>
+      </c>
+      <c r="K109" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109" t="s">
+        <v>658</v>
+      </c>
+      <c r="M109" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>660</v>
+      </c>
+      <c r="B110" t="s">
+        <v>661</v>
+      </c>
+      <c r="C110" t="s">
+        <v>662</v>
+      </c>
+      <c r="D110" t="s">
+        <v>663</v>
+      </c>
+      <c r="E110" t="s">
+        <v>599</v>
+      </c>
+      <c r="F110" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110" t="s">
+        <v>19</v>
+      </c>
+      <c r="H110" t="s">
+        <v>664</v>
+      </c>
+      <c r="I110" t="s">
+        <v>21</v>
+      </c>
+      <c r="J110" t="s">
+        <v>463</v>
+      </c>
+      <c r="K110" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110" t="s">
+        <v>665</v>
+      </c>
+      <c r="M110" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>667</v>
+      </c>
+      <c r="B111" t="s">
+        <v>668</v>
+      </c>
+      <c r="C111" t="s">
+        <v>669</v>
+      </c>
+      <c r="D111" t="s">
+        <v>670</v>
+      </c>
+      <c r="E111" t="s">
+        <v>599</v>
+      </c>
+      <c r="F111" t="s">
+        <v>18</v>
+      </c>
+      <c r="G111" t="s">
+        <v>19</v>
+      </c>
+      <c r="H111" t="s">
+        <v>103</v>
+      </c>
+      <c r="I111" t="s">
+        <v>21</v>
+      </c>
+      <c r="J111" t="s">
+        <v>671</v>
+      </c>
+      <c r="K111" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111" t="s">
+        <v>672</v>
+      </c>
+      <c r="M111" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>674</v>
+      </c>
+      <c r="B112" t="s">
+        <v>675</v>
+      </c>
+      <c r="C112" t="s">
+        <v>28</v>
+      </c>
+      <c r="D112" t="s">
+        <v>676</v>
+      </c>
+      <c r="E112" t="s">
+        <v>677</v>
+      </c>
+      <c r="F112" t="s">
+        <v>18</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" t="s">
+        <v>20</v>
+      </c>
+      <c r="I112" t="s">
+        <v>21</v>
+      </c>
+      <c r="J112" t="s">
+        <v>362</v>
+      </c>
+      <c r="K112" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112" t="s">
+        <v>678</v>
+      </c>
+      <c r="M112" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>680</v>
+      </c>
+      <c r="B113" t="s">
+        <v>681</v>
+      </c>
+      <c r="C113" t="s">
+        <v>28</v>
+      </c>
+      <c r="D113" t="s">
+        <v>682</v>
+      </c>
+      <c r="E113" t="s">
+        <v>677</v>
+      </c>
+      <c r="F113" t="s">
+        <v>18</v>
+      </c>
+      <c r="G113" t="s">
+        <v>19</v>
+      </c>
+      <c r="H113" t="s">
+        <v>51</v>
+      </c>
+      <c r="I113" t="s">
+        <v>21</v>
+      </c>
+      <c r="J113" t="s">
+        <v>64</v>
+      </c>
+      <c r="K113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113" t="s">
+        <v>683</v>
+      </c>
+      <c r="M113" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>685</v>
+      </c>
+      <c r="B114" t="s">
+        <v>686</v>
+      </c>
+      <c r="C114" t="s">
+        <v>28</v>
+      </c>
+      <c r="D114" t="s">
+        <v>687</v>
+      </c>
+      <c r="E114" t="s">
+        <v>677</v>
+      </c>
+      <c r="F114" t="s">
+        <v>18</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" t="s">
+        <v>336</v>
+      </c>
+      <c r="I114" t="s">
+        <v>21</v>
+      </c>
+      <c r="J114" t="s">
+        <v>122</v>
+      </c>
+      <c r="K114" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114" t="s">
+        <v>688</v>
+      </c>
+      <c r="M114" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>690</v>
+      </c>
+      <c r="B115" t="s">
+        <v>691</v>
+      </c>
+      <c r="C115" t="s">
+        <v>28</v>
+      </c>
+      <c r="D115" t="s">
+        <v>692</v>
+      </c>
+      <c r="E115" t="s">
+        <v>677</v>
+      </c>
+      <c r="F115" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" t="s">
+        <v>37</v>
+      </c>
+      <c r="I115" t="s">
+        <v>21</v>
+      </c>
+      <c r="J115" t="s">
+        <v>153</v>
+      </c>
+      <c r="K115" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115" t="s">
+        <v>693</v>
+      </c>
+      <c r="M115" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>695</v>
+      </c>
+      <c r="B116" t="s">
+        <v>696</v>
+      </c>
+      <c r="C116" t="s">
+        <v>299</v>
+      </c>
+      <c r="D116" t="s">
+        <v>697</v>
+      </c>
+      <c r="E116" t="s">
+        <v>677</v>
+      </c>
+      <c r="F116" t="s">
+        <v>18</v>
+      </c>
+      <c r="G116" t="s">
+        <v>19</v>
+      </c>
+      <c r="H116" t="s">
+        <v>51</v>
+      </c>
+      <c r="I116" t="s">
+        <v>21</v>
+      </c>
+      <c r="J116" t="s">
+        <v>64</v>
+      </c>
+      <c r="K116" t="s">
+        <v>23</v>
+      </c>
+      <c r="L116" t="s">
+        <v>698</v>
+      </c>
+      <c r="M116" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>700</v>
+      </c>
+      <c r="B117" t="s">
+        <v>701</v>
+      </c>
+      <c r="C117" t="s">
+        <v>299</v>
+      </c>
+      <c r="D117" t="s">
+        <v>702</v>
+      </c>
+      <c r="E117" t="s">
+        <v>677</v>
+      </c>
+      <c r="F117" t="s">
+        <v>18</v>
+      </c>
+      <c r="G117" t="s">
+        <v>19</v>
+      </c>
+      <c r="H117" t="s">
+        <v>51</v>
+      </c>
+      <c r="I117" t="s">
+        <v>395</v>
+      </c>
+      <c r="J117" t="s">
+        <v>310</v>
+      </c>
+      <c r="K117" t="s">
+        <v>23</v>
+      </c>
+      <c r="L117" t="s">
+        <v>703</v>
+      </c>
+      <c r="M117" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>705</v>
+      </c>
+      <c r="B118" t="s">
+        <v>706</v>
+      </c>
+      <c r="C118" t="s">
+        <v>81</v>
+      </c>
+      <c r="D118" t="s">
+        <v>707</v>
+      </c>
+      <c r="E118" t="s">
+        <v>677</v>
+      </c>
+      <c r="F118" t="s">
+        <v>18</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" t="s">
+        <v>317</v>
+      </c>
+      <c r="I118" t="s">
+        <v>21</v>
+      </c>
+      <c r="J118" t="s">
+        <v>64</v>
+      </c>
+      <c r="K118" t="s">
+        <v>23</v>
+      </c>
+      <c r="L118" t="s">
+        <v>708</v>
+      </c>
+      <c r="M118" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>710</v>
+      </c>
+      <c r="B119" t="s">
+        <v>711</v>
+      </c>
+      <c r="C119" t="s">
+        <v>28</v>
+      </c>
+      <c r="D119" t="s">
+        <v>712</v>
+      </c>
+      <c r="E119" t="s">
+        <v>677</v>
+      </c>
+      <c r="F119" t="s">
+        <v>18</v>
+      </c>
+      <c r="G119" t="s">
+        <v>19</v>
+      </c>
+      <c r="H119" t="s">
+        <v>64</v>
+      </c>
+      <c r="I119" t="s">
+        <v>211</v>
+      </c>
+      <c r="J119" t="s">
+        <v>64</v>
+      </c>
+      <c r="K119" t="s">
+        <v>23</v>
+      </c>
+      <c r="L119" t="s">
+        <v>713</v>
+      </c>
+      <c r="M119" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>715</v>
+      </c>
+      <c r="B120" t="s">
+        <v>716</v>
+      </c>
+      <c r="C120" t="s">
+        <v>299</v>
+      </c>
+      <c r="D120" t="s">
+        <v>717</v>
+      </c>
+      <c r="E120" t="s">
+        <v>677</v>
+      </c>
+      <c r="F120" t="s">
+        <v>18</v>
+      </c>
+      <c r="G120" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120" t="s">
+        <v>64</v>
+      </c>
+      <c r="I120" t="s">
+        <v>309</v>
+      </c>
+      <c r="J120" t="s">
+        <v>64</v>
+      </c>
+      <c r="K120" t="s">
+        <v>23</v>
+      </c>
+      <c r="L120" t="s">
+        <v>718</v>
+      </c>
+      <c r="M120" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>720</v>
+      </c>
+      <c r="B121" t="s">
+        <v>721</v>
+      </c>
+      <c r="C121" t="s">
+        <v>245</v>
+      </c>
+      <c r="D121" t="s">
+        <v>722</v>
+      </c>
+      <c r="E121" t="s">
+        <v>677</v>
+      </c>
+      <c r="F121" t="s">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>19</v>
+      </c>
+      <c r="H121" t="s">
+        <v>51</v>
+      </c>
+      <c r="I121" t="s">
+        <v>21</v>
+      </c>
+      <c r="J121" t="s">
+        <v>558</v>
+      </c>
+      <c r="K121" t="s">
+        <v>23</v>
+      </c>
+      <c r="L121" t="s">
+        <v>723</v>
+      </c>
+      <c r="M121" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>725</v>
+      </c>
+      <c r="B122" t="s">
+        <v>726</v>
+      </c>
+      <c r="C122" t="s">
+        <v>151</v>
+      </c>
+      <c r="D122" t="s">
+        <v>727</v>
+      </c>
+      <c r="E122" t="s">
+        <v>677</v>
+      </c>
+      <c r="F122" t="s">
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>19</v>
+      </c>
+      <c r="H122" t="s">
+        <v>51</v>
+      </c>
+      <c r="I122" t="s">
+        <v>21</v>
+      </c>
+      <c r="J122" t="s">
+        <v>178</v>
+      </c>
+      <c r="K122" t="s">
+        <v>23</v>
+      </c>
+      <c r="L122" t="s">
+        <v>728</v>
+      </c>
+      <c r="M122" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>730</v>
+      </c>
+      <c r="B123" t="s">
+        <v>731</v>
+      </c>
+      <c r="C123" t="s">
+        <v>28</v>
+      </c>
+      <c r="D123" t="s">
+        <v>732</v>
+      </c>
+      <c r="E123" t="s">
+        <v>677</v>
+      </c>
+      <c r="F123" t="s">
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>19</v>
+      </c>
+      <c r="H123" t="s">
+        <v>64</v>
+      </c>
+      <c r="I123" t="s">
+        <v>211</v>
+      </c>
+      <c r="J123" t="s">
+        <v>64</v>
+      </c>
+      <c r="K123" t="s">
+        <v>23</v>
+      </c>
+      <c r="L123" t="s">
+        <v>733</v>
+      </c>
+      <c r="M123" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>735</v>
+      </c>
+      <c r="B124" t="s">
+        <v>736</v>
+      </c>
+      <c r="C124" t="s">
+        <v>737</v>
+      </c>
+      <c r="D124" t="s">
+        <v>738</v>
+      </c>
+      <c r="E124" t="s">
+        <v>677</v>
+      </c>
+      <c r="F124" t="s">
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>19</v>
+      </c>
+      <c r="H124" t="s">
+        <v>51</v>
+      </c>
+      <c r="I124" t="s">
+        <v>21</v>
+      </c>
+      <c r="J124" t="s">
+        <v>64</v>
+      </c>
+      <c r="K124" t="s">
+        <v>23</v>
+      </c>
+      <c r="L124" t="s">
+        <v>739</v>
+      </c>
+      <c r="M124" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>741</v>
+      </c>
+      <c r="B125" t="s">
+        <v>742</v>
+      </c>
+      <c r="C125" t="s">
+        <v>28</v>
+      </c>
+      <c r="D125" t="s">
+        <v>743</v>
+      </c>
+      <c r="E125" t="s">
+        <v>677</v>
+      </c>
+      <c r="F125" t="s">
+        <v>18</v>
+      </c>
+      <c r="G125" t="s">
+        <v>19</v>
+      </c>
+      <c r="H125" t="s">
+        <v>64</v>
+      </c>
+      <c r="I125" t="s">
+        <v>211</v>
+      </c>
+      <c r="J125" t="s">
+        <v>744</v>
+      </c>
+      <c r="K125" t="s">
+        <v>23</v>
+      </c>
+      <c r="L125" t="s">
+        <v>745</v>
+      </c>
+      <c r="M125" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>747</v>
+      </c>
+      <c r="B126" t="s">
+        <v>748</v>
+      </c>
+      <c r="C126" t="s">
+        <v>749</v>
+      </c>
+      <c r="D126" t="s">
+        <v>750</v>
+      </c>
+      <c r="E126" t="s">
+        <v>677</v>
+      </c>
+      <c r="F126" t="s">
+        <v>18</v>
+      </c>
+      <c r="G126" t="s">
+        <v>19</v>
+      </c>
+      <c r="H126" t="s">
+        <v>20</v>
+      </c>
+      <c r="I126" t="s">
+        <v>21</v>
+      </c>
+      <c r="J126" t="s">
+        <v>751</v>
+      </c>
+      <c r="K126" t="s">
+        <v>23</v>
+      </c>
+      <c r="L126" t="s">
+        <v>752</v>
+      </c>
+      <c r="M126" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>754</v>
+      </c>
+      <c r="B127" t="s">
+        <v>755</v>
+      </c>
+      <c r="C127" t="s">
+        <v>756</v>
+      </c>
+      <c r="D127" t="s">
+        <v>757</v>
+      </c>
+      <c r="E127" t="s">
+        <v>677</v>
+      </c>
+      <c r="F127" t="s">
+        <v>18</v>
+      </c>
+      <c r="G127" t="s">
+        <v>19</v>
+      </c>
+      <c r="H127" t="s">
+        <v>234</v>
+      </c>
+      <c r="I127" t="s">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s">
+        <v>744</v>
+      </c>
+      <c r="K127" t="s">
+        <v>23</v>
+      </c>
+      <c r="L127" t="s">
+        <v>758</v>
+      </c>
+      <c r="M127" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>760</v>
+      </c>
+      <c r="B128" t="s">
+        <v>761</v>
+      </c>
+      <c r="C128" t="s">
+        <v>28</v>
+      </c>
+      <c r="D128" t="s">
+        <v>762</v>
+      </c>
+      <c r="E128" t="s">
+        <v>763</v>
+      </c>
+      <c r="F128" t="s">
+        <v>18</v>
+      </c>
+      <c r="G128" t="s">
+        <v>19</v>
+      </c>
+      <c r="H128" t="s">
+        <v>51</v>
+      </c>
+      <c r="I128" t="s">
+        <v>21</v>
+      </c>
+      <c r="J128" t="s">
+        <v>160</v>
+      </c>
+      <c r="K128" t="s">
+        <v>23</v>
+      </c>
+      <c r="L128" t="s">
+        <v>764</v>
+      </c>
+      <c r="M128" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>766</v>
+      </c>
+      <c r="B129" t="s">
+        <v>767</v>
+      </c>
+      <c r="C129" t="s">
+        <v>28</v>
+      </c>
+      <c r="D129" t="s">
+        <v>768</v>
+      </c>
+      <c r="E129" t="s">
+        <v>763</v>
+      </c>
+      <c r="F129" t="s">
+        <v>18</v>
+      </c>
+      <c r="G129" t="s">
+        <v>19</v>
+      </c>
+      <c r="H129" t="s">
+        <v>336</v>
+      </c>
+      <c r="I129" t="s">
+        <v>21</v>
+      </c>
+      <c r="J129" t="s">
+        <v>485</v>
+      </c>
+      <c r="K129" t="s">
+        <v>23</v>
+      </c>
+      <c r="L129" t="s">
+        <v>769</v>
+      </c>
+      <c r="M129" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>771</v>
+      </c>
+      <c r="B130" t="s">
+        <v>772</v>
+      </c>
+      <c r="C130" t="s">
+        <v>245</v>
+      </c>
+      <c r="D130" t="s">
+        <v>773</v>
+      </c>
+      <c r="E130" t="s">
+        <v>763</v>
+      </c>
+      <c r="F130" t="s">
+        <v>18</v>
+      </c>
+      <c r="G130" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" t="s">
+        <v>37</v>
+      </c>
+      <c r="I130" t="s">
+        <v>21</v>
+      </c>
+      <c r="J130" t="s">
+        <v>774</v>
+      </c>
+      <c r="K130" t="s">
+        <v>23</v>
+      </c>
+      <c r="L130" t="s">
+        <v>775</v>
+      </c>
+      <c r="M130" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>777</v>
+      </c>
+      <c r="B131" t="s">
+        <v>778</v>
+      </c>
+      <c r="C131" t="s">
+        <v>28</v>
+      </c>
+      <c r="D131" t="s">
+        <v>779</v>
+      </c>
+      <c r="E131" t="s">
+        <v>780</v>
+      </c>
+      <c r="F131" t="s">
+        <v>18</v>
+      </c>
+      <c r="G131" t="s">
+        <v>19</v>
+      </c>
+      <c r="H131" t="s">
+        <v>51</v>
+      </c>
+      <c r="I131" t="s">
+        <v>21</v>
+      </c>
+      <c r="J131" t="s">
+        <v>463</v>
+      </c>
+      <c r="K131" t="s">
+        <v>23</v>
+      </c>
+      <c r="L131" t="s">
+        <v>781</v>
+      </c>
+      <c r="M131" t="s">
+        <v>782</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>783</v>
+      </c>
+      <c r="B132" t="s">
+        <v>784</v>
+      </c>
+      <c r="C132" t="s">
+        <v>28</v>
+      </c>
+      <c r="D132" t="s">
+        <v>785</v>
+      </c>
+      <c r="E132" t="s">
+        <v>763</v>
+      </c>
+      <c r="F132" t="s">
+        <v>18</v>
+      </c>
+      <c r="G132" t="s">
+        <v>19</v>
+      </c>
+      <c r="H132" t="s">
+        <v>51</v>
+      </c>
+      <c r="I132" t="s">
+        <v>21</v>
+      </c>
+      <c r="J132" t="s">
+        <v>64</v>
+      </c>
+      <c r="K132" t="s">
+        <v>23</v>
+      </c>
+      <c r="L132" t="s">
+        <v>786</v>
+      </c>
+      <c r="M132" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>788</v>
+      </c>
+      <c r="B133" t="s">
+        <v>789</v>
+      </c>
+      <c r="C133" t="s">
+        <v>151</v>
+      </c>
+      <c r="D133" t="s">
+        <v>790</v>
+      </c>
+      <c r="E133" t="s">
+        <v>780</v>
+      </c>
+      <c r="F133" t="s">
+        <v>18</v>
+      </c>
+      <c r="G133" t="s">
+        <v>19</v>
+      </c>
+      <c r="H133" t="s">
+        <v>51</v>
+      </c>
+      <c r="I133" t="s">
+        <v>21</v>
+      </c>
+      <c r="J133" t="s">
+        <v>369</v>
+      </c>
+      <c r="K133" t="s">
+        <v>23</v>
+      </c>
+      <c r="L133" t="s">
+        <v>791</v>
+      </c>
+      <c r="M133" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>793</v>
+      </c>
+      <c r="B134" t="s">
+        <v>794</v>
+      </c>
+      <c r="C134" t="s">
+        <v>28</v>
+      </c>
+      <c r="D134" t="s">
+        <v>795</v>
+      </c>
+      <c r="E134" t="s">
+        <v>780</v>
+      </c>
+      <c r="F134" t="s">
+        <v>18</v>
+      </c>
+      <c r="G134" t="s">
+        <v>19</v>
+      </c>
+      <c r="H134" t="s">
+        <v>51</v>
+      </c>
+      <c r="I134" t="s">
+        <v>21</v>
+      </c>
+      <c r="J134" t="s">
+        <v>64</v>
+      </c>
+      <c r="K134" t="s">
+        <v>23</v>
+      </c>
+      <c r="L134" t="s">
+        <v>796</v>
+      </c>
+      <c r="M134" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>798</v>
+      </c>
+      <c r="B135" t="s">
+        <v>799</v>
+      </c>
+      <c r="C135" t="s">
+        <v>468</v>
+      </c>
+      <c r="D135" t="s">
+        <v>800</v>
+      </c>
+      <c r="E135" t="s">
+        <v>780</v>
+      </c>
+      <c r="F135" t="s">
+        <v>18</v>
+      </c>
+      <c r="G135" t="s">
+        <v>19</v>
+      </c>
+      <c r="H135" t="s">
+        <v>64</v>
+      </c>
+      <c r="I135" t="s">
+        <v>211</v>
+      </c>
+      <c r="J135" t="s">
+        <v>64</v>
+      </c>
+      <c r="K135" t="s">
+        <v>23</v>
+      </c>
+      <c r="L135" t="s">
+        <v>801</v>
+      </c>
+      <c r="M135" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>803</v>
+      </c>
+      <c r="B136" t="s">
+        <v>804</v>
+      </c>
+      <c r="C136" t="s">
+        <v>805</v>
+      </c>
+      <c r="D136" t="s">
+        <v>806</v>
+      </c>
+      <c r="E136" t="s">
+        <v>780</v>
+      </c>
+      <c r="F136" t="s">
+        <v>18</v>
+      </c>
+      <c r="G136" t="s">
+        <v>19</v>
+      </c>
+      <c r="H136" t="s">
+        <v>64</v>
+      </c>
+      <c r="I136" t="s">
+        <v>211</v>
+      </c>
+      <c r="J136" t="s">
+        <v>64</v>
+      </c>
+      <c r="K136" t="s">
+        <v>23</v>
+      </c>
+      <c r="L136" t="s">
+        <v>807</v>
+      </c>
+      <c r="M136" t="s">
+        <v>808</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
